--- a/contest_entry_forms/014_talent_show_auditions_sign_up_form--contest_entry_forms.xlsx
+++ b/contest_entry_forms/014_talent_show_auditions_sign_up_form--contest_entry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -904,12 +904,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>performer_name</t>
+          <t>performer_name_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>performer name</t>
+          <t>Performer Name 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_phone_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Parent Contact Phone</t>
+          <t>Contact Phone 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_email_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>act_type</t>
+          <t>act_type_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Type of Act</t>
+          <t>Act Type 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>contact_note</t>
+          <t>contact_note_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Contact Note 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>performer_address</t>
+          <t>performer_address_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>performer address</t>
+          <t>Performer Address 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contact_phone_ext</t>
+          <t>contact_phone_ext_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>contact_email_ext</t>
+          <t>contact_email_ext_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Parent Contact Email Ext</t>
+          <t>Contact Email Ext 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>act_note</t>
+          <t>act_note_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Act Notes</t>
+          <t>Act Note 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1210,17 +1210,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>act_type_choices</t>
+          <t>contact_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dancer</t>
+          <t>8_to_10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dancer</t>
+          <t>8 to 10</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8_to_10</t>
+          <t>11_to_20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8 to 10</t>
+          <t>11 to 20</t>
         </is>
       </c>
     </row>
@@ -1249,197 +1249,180 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11_to_20</t>
+          <t>21_to_30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11 to 20</t>
+          <t>21 to 30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contact_choices</t>
+          <t>performer_name_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21_to_30</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21 to 30</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>performer_name_choices</t>
+          <t>performer_name_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>performer_name_choices</t>
+          <t>act_type_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>singer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Singer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>act_type_choices</t>
+          <t>act_type_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>singer</t>
+          <t>dancer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singer</t>
+          <t>Dancer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>act_type_choices</t>
+          <t>act_type_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dancer</t>
+          <t>instrumentalist</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dancer</t>
+          <t>Instrumentalist</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>act_type_choices</t>
+          <t>act_type_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>instrumentalist</t>
+          <t>comedian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Instrumentalist</t>
+          <t>Comedian</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>act_type_choices</t>
+          <t>act_type_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comedian</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comedian</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>act_type_choices</t>
+          <t>act_type_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>drama</t>
+          <t>juggler</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Drama</t>
+          <t>Juggler</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>act_type_choices</t>
+          <t>act_type_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>juggler</t>
+          <t>clown</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Juggler</t>
+          <t>Clown</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>act_type_choices</t>
+          <t>act_type_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>clown</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Clown</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>act_type_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
